--- a/data/trans_camb/IP1014-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,0</t>
+          <t>-3,77; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,0</t>
+          <t>-3,19; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,94</t>
+          <t>-1,48; 2,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,86</t>
+          <t>-1,48; 3,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,36</t>
+          <t>-2,18; 0,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,54</t>
+          <t>-1,45; 1,47</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,04</t>
+          <t>-0,47; 1,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,37</t>
+          <t>-0,88; 0,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,72</t>
+          <t>-0,24; 0,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,2</t>
+          <t>-0,48; 0,15</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-68,88; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,47; 1197,22</t>
+          <t>-69,57; 1000,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,17 +953,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,4</t>
+          <t>-0,86; 1,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,0</t>
+          <t>-2,14; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,91</t>
+          <t>-0,41; 0,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,53</t>
+          <t>-0,19; 0,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,55; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,88</t>
+          <t>-0,5; 0,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,25</t>
+          <t>-0,76; 0,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,49</t>
+          <t>-0,23; 0,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,1</t>
+          <t>-0,49; 0,09</t>
         </is>
       </c>
     </row>
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,4; 469,52</t>
+          <t>-71,14; 417,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 179,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,53; 385,79</t>
+          <t>-60,56; 410,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 107,0</t>
+          <t>-100,0; 144,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1014-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,0</t>
+          <t>-2,88; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,0</t>
+          <t>-2,85; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,99</t>
+          <t>-1,48; 2,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,6</t>
+          <t>-1,49; 3,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,7</t>
+          <t>-2,16; 0,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,47</t>
+          <t>-1,46; 1,35</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,03</t>
+          <t>-0,46; 1,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,67</t>
+          <t>-0,23; 0,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,15</t>
+          <t>-0,54; 0,2</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-68,88; —</t>
+          <t>-80,39; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,57; 1000,47</t>
+          <t>-68,09; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,17 +953,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,41</t>
+          <t>-0,85; 1,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,0</t>
+          <t>-2,15; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,97</t>
+          <t>-0,41; 0,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,51</t>
+          <t>-0,19; 0,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,0</t>
+          <t>-0,5; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,76</t>
+          <t>-0,41; 0,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,25</t>
+          <t>-0,77; 0,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,5</t>
+          <t>-0,21; 0,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,09</t>
+          <t>-0,48; 0,08</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-71,14; 417,36</t>
+          <t>-61,43; 535,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,56; 410,33</t>
+          <t>-59,2; 312,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 144,14</t>
+          <t>-100,0; 114,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1014-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-0,71</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,71</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,0</t>
+          <t>-1,49; 2,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,0</t>
+          <t>-1,48; 3,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,27</t>
+          <t>-4,61; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,62</t>
+          <t>-3,55; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,7</t>
+          <t>-1,82; 0,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,35</t>
+          <t>-1,46; 1,54</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30,52%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30,52%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,16</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>-0,47; 1,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,88; 0,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,06</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,7</t>
+          <t>-0,23; 0,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,2</t>
+          <t>-0,47; 0,2</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52,21%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-37,58%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>52,21%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-37,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,39; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,09; —</t>
+          <t>-68,47; 1197,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,04</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,27 +943,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>-0,86; 1,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,73; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,39</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,96</t>
+          <t>-0,41; 0,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,09</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,57</t>
+          <t>-0,45; 0,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,0</t>
+          <t>-0,77; 0,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,84</t>
+          <t>-0,16; 0,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,19</t>
+          <t>-0,47; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,48</t>
+          <t>-0,23; 0,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,08</t>
+          <t>-0,48; 0,1</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-43,11%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>100,93%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-43,11%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-66,4; 469,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 179,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,43; 535,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,2; 312,77</t>
+          <t>-56,53; 385,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 114,18</t>
+          <t>-100,0; 107,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1014-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,271 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.007020690460689694</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2256377186268909</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.7062861718131215</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.7062861718131215</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.3670261532132572</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.2051334946696928</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-1,49; 2,94</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-1,48; 3,86</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,61; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-3,55; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-1,82; 0,36</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-1,46; 1,54</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.487661355199967</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.481441606879387</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.606213835576606</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.554580446855186</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-1.815901724608152</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-1.455039454669851</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>30,52%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-50,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-28,39%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.935644464990816</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.862903819252955</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.3638392361575408</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1.539290191325572</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.009495561825441748</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.3051775205544088</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.5080288296535754</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2839408807994114</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,47; 1,04</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,88; 0,37</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,23; 0,72</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,47; 0,2</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>52,21%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-37,58%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>89,69%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-40,56%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.2280980226502036</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.1641883362408624</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1991930861191272</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.2093053173763368</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.0946583911616266</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-68,47; 1197,22</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.4699137870737322</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.880235934154756</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="n">
+        <v>-0.2301849906920731</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.4657259734278298</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.040349867173527</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.3725833376835511</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9994784933781297</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="n">
+        <v>0.7175289600776076</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.199534071393556</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,86; 1,4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,73; 0,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,3</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-0,41; 0,91</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-1,02; 0,0</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.5220658985649436</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.3757907687999521</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="n">
+        <v>0.8969404425450769</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.4056415781661987</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>81,08%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>-0.6847118070973498</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>11.97221974030897</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +872,281 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0.03677740908034728</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.4256821102391004</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.2678300614319545</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.1643056503499704</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.2026360666034461</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,45; 0,88</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,77; 0,25</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,16; 0,53</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,47; 0,0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-0,23; 0,49</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-0,48; 0,1</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.8566130533244103</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.727857627457533</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="n">
+        <v>-0.408766503960463</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-1.017973800121399</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-43,11%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>100,93%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>43,94%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-52,21%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.401376737816371</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.29607633048371</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="n">
+        <v>0.9095980902139666</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-66,4; 469,52</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 179,1</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-56,53; 385,79</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 107,0</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.08639641694054247</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="n">
+        <v>0.8108410960794682</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.156782597934998</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.2029890891624652</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.09511632098986256</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.09423824374392711</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.1265660487269368</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.1503698473159902</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.4548905609698445</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.7723750212799395</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.1584708891947864</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.4719070718206798</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.2267895056582911</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.4831689730441781</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.8775977524525019</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.2520051706227386</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.5348922477054412</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.4856164847836368</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.09694714781629664</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0.3329883097710433</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.4311256133808737</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>1.009317631685937</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.4394150810083368</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.5220576869087683</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-0.6639931419383543</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>-0.5653243881133398</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>4.69523395128054</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>1.790960088646953</v>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>3.857926916820696</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1.069967613197853</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1154,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
